--- a/src/attributions/attributions_saliency_traj_76.xlsx
+++ b/src/attributions/attributions_saliency_traj_76.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG3"/>
+  <dimension ref="A1:GG16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,1139 +999,8536 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8.50811204600177e-07</v>
+        <v>0.03346788883209229</v>
       </c>
       <c r="B2" t="n">
-        <v>8.839213478495367e-06</v>
+        <v>0.9480788707733154</v>
       </c>
       <c r="C2" t="n">
-        <v>2.294643309141975e-06</v>
+        <v>0.01112257689237595</v>
       </c>
       <c r="D2" t="n">
-        <v>1.340384824288776e-05</v>
+        <v>0.133072704076767</v>
       </c>
       <c r="E2" t="n">
-        <v>4.681493919633795e-06</v>
+        <v>0.5599154829978943</v>
       </c>
       <c r="F2" t="n">
-        <v>2.035420038737357e-06</v>
+        <v>0.1813904196023941</v>
       </c>
       <c r="G2" t="n">
-        <v>2.79270807368448e-06</v>
+        <v>0.2859334051609039</v>
       </c>
       <c r="H2" t="n">
-        <v>2.649369662321988e-06</v>
+        <v>0.004343327134847641</v>
       </c>
       <c r="I2" t="n">
-        <v>2.176171392420656e-06</v>
+        <v>0.2029988318681717</v>
       </c>
       <c r="J2" t="n">
-        <v>2.083198069158243e-06</v>
+        <v>0.1190711110830307</v>
       </c>
       <c r="K2" t="n">
-        <v>1.052092466125032e-05</v>
+        <v>0.6371936798095703</v>
       </c>
       <c r="L2" t="n">
-        <v>3.722294650287949e-07</v>
+        <v>0.2257925868034363</v>
       </c>
       <c r="M2" t="n">
-        <v>1.441560198145453e-05</v>
+        <v>0.3862046599388123</v>
       </c>
       <c r="N2" t="n">
-        <v>3.44640602634172e-06</v>
+        <v>0.8089466094970703</v>
       </c>
       <c r="O2" t="n">
-        <v>7.210991952888435e-06</v>
+        <v>0.0105929896235466</v>
       </c>
       <c r="P2" t="n">
-        <v>2.876204234780744e-06</v>
+        <v>0.03411534428596497</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.467566213861573e-06</v>
+        <v>0.0566718615591526</v>
       </c>
       <c r="R2" t="n">
-        <v>3.744614332390483e-06</v>
+        <v>0.4176068007946014</v>
       </c>
       <c r="S2" t="n">
-        <v>2.849768634405336e-06</v>
+        <v>0.04100026190280914</v>
       </c>
       <c r="T2" t="n">
-        <v>3.199328602931928e-06</v>
+        <v>0.09518235176801682</v>
       </c>
       <c r="U2" t="n">
-        <v>4.420900552304374e-07</v>
+        <v>0.006061991676688194</v>
       </c>
       <c r="V2" t="n">
-        <v>9.620059699955164e-07</v>
+        <v>0.1507198959589005</v>
       </c>
       <c r="W2" t="n">
-        <v>4.852545771427685e-06</v>
+        <v>0.003928877413272858</v>
       </c>
       <c r="X2" t="n">
-        <v>1.533534373265866e-06</v>
+        <v>0.4883272051811218</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.072360530291917e-06</v>
+        <v>0.0076003298163414</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.803835968734347e-06</v>
+        <v>0.2972046136856079</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.509166850155452e-06</v>
+        <v>0.2202208489179611</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.022390723752324e-06</v>
+        <v>0.1617011278867722</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.939214371304843e-06</v>
+        <v>0.02599810808897018</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.164019522548188e-06</v>
+        <v>0.1821495294570923</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.96142286263057e-06</v>
+        <v>0.0469607412815094</v>
       </c>
       <c r="AF2" t="n">
-        <v>3.209864189557265e-06</v>
+        <v>0.1847719252109528</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.599793336026778e-06</v>
+        <v>0.2036216557025909</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.145271992048947e-06</v>
+        <v>0.09564684331417084</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.120667434406641e-06</v>
+        <v>0.004835758358240128</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.063703732346767e-06</v>
+        <v>0.01425757072865963</v>
       </c>
       <c r="AK2" t="n">
-        <v>4.042679393023718e-06</v>
+        <v>0.09332610666751862</v>
       </c>
       <c r="AL2" t="n">
-        <v>6.070541985536693e-06</v>
+        <v>0.3532885909080505</v>
       </c>
       <c r="AM2" t="n">
-        <v>5.048888169767451e-07</v>
+        <v>0.05731729790568352</v>
       </c>
       <c r="AN2" t="n">
-        <v>3.3871071991598e-06</v>
+        <v>0.030406653881073</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.886908989945368e-06</v>
+        <v>0.6087693572044373</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.354105496735428e-07</v>
+        <v>0.1124544441699982</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.766446757756057e-07</v>
+        <v>0.09159518778324127</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.255990350226057e-06</v>
+        <v>0.04577303305268288</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.820552122619119e-07</v>
+        <v>0.2507023513317108</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.653377800423186e-06</v>
+        <v>0.02551223710179329</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.030621655852883e-06</v>
+        <v>0.4127933382987976</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.410806416719424e-07</v>
+        <v>0.04779788851737976</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.702173787838547e-06</v>
+        <v>0.07104555517435074</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.480871886400564e-07</v>
+        <v>0.2493064403533936</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.165809630445438e-06</v>
+        <v>0.2155803292989731</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.640694901856477e-06</v>
+        <v>0.003338666632771492</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.631845164723927e-07</v>
+        <v>0.3001840114593506</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.582443360348407e-06</v>
+        <v>0.1918337792158127</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.252719799704209e-07</v>
+        <v>0.2398940771818161</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.32780245016329e-06</v>
+        <v>0.2017035186290741</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.372285396428197e-06</v>
+        <v>0.100732296705246</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.053090484987479e-06</v>
+        <v>0.02727445960044861</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.730536364964792e-07</v>
+        <v>0.1999356299638748</v>
       </c>
       <c r="BH2" t="n">
-        <v>1.369748702018114e-06</v>
+        <v>0.2667361497879028</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.813371568459843e-06</v>
+        <v>0.4867649972438812</v>
       </c>
       <c r="BJ2" t="n">
-        <v>3.774544552470616e-07</v>
+        <v>0.0870080292224884</v>
       </c>
       <c r="BK2" t="n">
-        <v>2.223554929514648e-06</v>
+        <v>0.347732812166214</v>
       </c>
       <c r="BL2" t="n">
-        <v>5.732806130254176e-06</v>
+        <v>0.1185458600521088</v>
       </c>
       <c r="BM2" t="n">
-        <v>5.57831617697957e-06</v>
+        <v>0.2963978946208954</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.903240445244592e-07</v>
+        <v>0.04406234249472618</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.50061043768801e-06</v>
+        <v>0.3163133859634399</v>
       </c>
       <c r="BP2" t="n">
-        <v>2.181400304834824e-06</v>
+        <v>0.1567016839981079</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2.397914329321793e-07</v>
+        <v>0.3720332682132721</v>
       </c>
       <c r="BR2" t="n">
-        <v>1.634305135667091e-07</v>
+        <v>0.1534239500761032</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.851814772635407e-07</v>
+        <v>0.1242599561810493</v>
       </c>
       <c r="BT2" t="n">
-        <v>1.30565990730247e-06</v>
+        <v>0.1387756317853928</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.982534508395474e-06</v>
+        <v>0.057122852653265</v>
       </c>
       <c r="BV2" t="n">
-        <v>2.431743723718682e-06</v>
+        <v>0.2882907688617706</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.143991413409822e-07</v>
+        <v>0.1711893081665039</v>
       </c>
       <c r="BX2" t="n">
-        <v>7.185419690358685e-07</v>
+        <v>0.1496893167495728</v>
       </c>
       <c r="BY2" t="n">
-        <v>5.451582637761021e-06</v>
+        <v>0.05731060355901718</v>
       </c>
       <c r="BZ2" t="n">
-        <v>8.790456718088535e-08</v>
+        <v>0.2950392663478851</v>
       </c>
       <c r="CA2" t="n">
-        <v>2.455874437146122e-06</v>
+        <v>0.01093380525708199</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.608848260228115e-07</v>
+        <v>0.08872516453266144</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.324342060295749e-06</v>
+        <v>0.1873711049556732</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.239833404222736e-06</v>
+        <v>0.06131506711244583</v>
       </c>
       <c r="CE2" t="n">
-        <v>2.694625891308533e-07</v>
+        <v>0.3006758093833923</v>
       </c>
       <c r="CF2" t="n">
-        <v>5.345118552213535e-07</v>
+        <v>0.0165677722543478</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.421109113332932e-06</v>
+        <v>0.03633959591388702</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.719158944979426e-06</v>
+        <v>0.002814819104969501</v>
       </c>
       <c r="CI2" t="n">
-        <v>5.062010473011469e-07</v>
+        <v>0.0450008362531662</v>
       </c>
       <c r="CJ2" t="n">
-        <v>4.236734412188525e-07</v>
+        <v>0.0004388764500617981</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.02438229987456e-06</v>
+        <v>0.09976337850093842</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.259835471500992e-07</v>
+        <v>0.03912999853491783</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.684497985683265e-06</v>
+        <v>0.05946227163076401</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.067400146188447e-06</v>
+        <v>0.3818604052066803</v>
       </c>
       <c r="CO2" t="n">
-        <v>5.219438321546477e-07</v>
+        <v>0.2042955905199051</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.323587639490142e-06</v>
+        <v>0.1515322625637054</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.104601660197659e-07</v>
+        <v>0.471819281578064</v>
       </c>
       <c r="CR2" t="n">
-        <v>6.072277187740838e-07</v>
+        <v>0.4124281108379364</v>
       </c>
       <c r="CS2" t="n">
-        <v>4.334252935223049e-06</v>
+        <v>0.1542085707187653</v>
       </c>
       <c r="CT2" t="n">
-        <v>5.274448085401673e-06</v>
+        <v>0.05769169330596924</v>
       </c>
       <c r="CU2" t="n">
-        <v>7.161659596022218e-06</v>
+        <v>0.006602004170417786</v>
       </c>
       <c r="CV2" t="n">
-        <v>3.21104653266957e-06</v>
+        <v>0.07005782425403595</v>
       </c>
       <c r="CW2" t="n">
-        <v>3.883306192165037e-07</v>
+        <v>0.3093825578689575</v>
       </c>
       <c r="CX2" t="n">
-        <v>4.009680480976385e-07</v>
+        <v>0.03226862847805023</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.671268475751276e-06</v>
+        <v>0.04143418371677399</v>
       </c>
       <c r="CZ2" t="n">
-        <v>7.591654025418393e-07</v>
+        <v>0.06960950791835785</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.116973749049066e-06</v>
+        <v>0.05556114017963409</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.126281858887523e-07</v>
+        <v>0.06010602787137032</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.374333010062401e-06</v>
+        <v>0.06113182753324509</v>
       </c>
       <c r="DD2" t="n">
-        <v>6.442469668854756e-09</v>
+        <v>0.002552992198616266</v>
       </c>
       <c r="DE2" t="n">
-        <v>8.71659494805499e-07</v>
+        <v>0.01659287512302399</v>
       </c>
       <c r="DF2" t="n">
-        <v>7.498016657336848e-06</v>
+        <v>0.248013824224472</v>
       </c>
       <c r="DG2" t="n">
-        <v>4.412045655044494e-06</v>
+        <v>0.08297387510538101</v>
       </c>
       <c r="DH2" t="n">
-        <v>3.247218273827457e-06</v>
+        <v>0.2465991973876953</v>
       </c>
       <c r="DI2" t="n">
-        <v>4.295642611396033e-06</v>
+        <v>0.09071093052625656</v>
       </c>
       <c r="DJ2" t="n">
-        <v>4.829075351153733e-06</v>
+        <v>0.1097662001848221</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.446736279031029e-06</v>
+        <v>0.06936432421207428</v>
       </c>
       <c r="DL2" t="n">
-        <v>1.220905573973141e-06</v>
+        <v>0.02429742924869061</v>
       </c>
       <c r="DM2" t="n">
-        <v>3.372478431629133e-06</v>
+        <v>0.02226438373327255</v>
       </c>
       <c r="DN2" t="n">
-        <v>2.323112084923196e-06</v>
+        <v>0.1364244818687439</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.384856998105533e-06</v>
+        <v>0.2698267996311188</v>
       </c>
       <c r="DP2" t="n">
-        <v>5.12728001922369e-06</v>
+        <v>0.08564727753400803</v>
       </c>
       <c r="DQ2" t="n">
-        <v>6.521312116092304e-06</v>
+        <v>0.5125730037689209</v>
       </c>
       <c r="DR2" t="n">
-        <v>3.555922376108356e-06</v>
+        <v>0.03960304334759712</v>
       </c>
       <c r="DS2" t="n">
-        <v>2.101086920447415e-06</v>
+        <v>0.03175025805830956</v>
       </c>
       <c r="DT2" t="n">
-        <v>6.424477874134027e-07</v>
+        <v>0.04490827769041061</v>
       </c>
       <c r="DU2" t="n">
-        <v>4.94455548505357e-07</v>
+        <v>0.07548674941062927</v>
       </c>
       <c r="DV2" t="n">
-        <v>1.30972409806418e-06</v>
+        <v>0.2096222937107086</v>
       </c>
       <c r="DW2" t="n">
-        <v>5.233857336861547e-06</v>
+        <v>0.1072591170668602</v>
       </c>
       <c r="DX2" t="n">
-        <v>2.776810788418516e-06</v>
+        <v>0.161766842007637</v>
       </c>
       <c r="DY2" t="n">
-        <v>1.138774109676888e-06</v>
+        <v>0.0397857278585434</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.617408538048039e-06</v>
+        <v>0.51465904712677</v>
       </c>
       <c r="EA2" t="n">
-        <v>9.60035663410963e-07</v>
+        <v>0.3071416914463043</v>
       </c>
       <c r="EB2" t="n">
-        <v>5.788498128822539e-06</v>
+        <v>0.2727825343608856</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.0078301215799e-07</v>
+        <v>0.08177011460065842</v>
       </c>
       <c r="ED2" t="n">
-        <v>2.351581997572794e-06</v>
+        <v>0.2136462777853012</v>
       </c>
       <c r="EE2" t="n">
-        <v>1.886764266600949e-06</v>
+        <v>0.01301605254411697</v>
       </c>
       <c r="EF2" t="n">
-        <v>1.165568392025307e-06</v>
+        <v>0.06665574014186859</v>
       </c>
       <c r="EG2" t="n">
-        <v>5.980939477012726e-07</v>
+        <v>0.3205985724925995</v>
       </c>
       <c r="EH2" t="n">
-        <v>7.936753263493301e-07</v>
+        <v>0.04926440864801407</v>
       </c>
       <c r="EI2" t="n">
-        <v>6.927184585947543e-06</v>
+        <v>0.8191826343536377</v>
       </c>
       <c r="EJ2" t="n">
-        <v>5.416148241010887e-08</v>
+        <v>0.1405927985906601</v>
       </c>
       <c r="EK2" t="n">
-        <v>6.142720394564094e-07</v>
+        <v>0.002101752907037735</v>
       </c>
       <c r="EL2" t="n">
-        <v>7.24171741239843e-07</v>
+        <v>0.01917952857911587</v>
       </c>
       <c r="EM2" t="n">
-        <v>2.345117763979943e-06</v>
+        <v>0.0005987532204017043</v>
       </c>
       <c r="EN2" t="n">
-        <v>1.242997541339719e-06</v>
+        <v>0.1572810411453247</v>
       </c>
       <c r="EO2" t="n">
-        <v>4.124041879549623e-06</v>
+        <v>0.04566290974617004</v>
       </c>
       <c r="EP2" t="n">
-        <v>1.642652364353125e-06</v>
+        <v>0.2190676033496857</v>
       </c>
       <c r="EQ2" t="n">
-        <v>4.247401193424594e-06</v>
+        <v>0.1435537040233612</v>
       </c>
       <c r="ER2" t="n">
-        <v>2.946404720205464e-06</v>
+        <v>0.2032038569450378</v>
       </c>
       <c r="ES2" t="n">
-        <v>4.209217649986385e-07</v>
+        <v>0.08062494546175003</v>
       </c>
       <c r="ET2" t="n">
-        <v>3.21592756336031e-06</v>
+        <v>0.1765325367450714</v>
       </c>
       <c r="EU2" t="n">
-        <v>6.702102837152779e-07</v>
+        <v>0.02617350593209267</v>
       </c>
       <c r="EV2" t="n">
-        <v>1.994938884308795e-06</v>
+        <v>0.0551268681883812</v>
       </c>
       <c r="EW2" t="n">
-        <v>9.344657314613869e-07</v>
+        <v>0.2003534287214279</v>
       </c>
       <c r="EX2" t="n">
-        <v>3.954515705117956e-06</v>
+        <v>0.0701148509979248</v>
       </c>
       <c r="EY2" t="n">
-        <v>4.074821049471211e-07</v>
+        <v>0.3498029410839081</v>
       </c>
       <c r="EZ2" t="n">
-        <v>4.565748099594202e-07</v>
+        <v>0.02532845176756382</v>
       </c>
       <c r="FA2" t="n">
-        <v>3.253088380006375e-06</v>
+        <v>0.07490827888250351</v>
       </c>
       <c r="FB2" t="n">
-        <v>1.589070052432362e-06</v>
+        <v>0.05811208486557007</v>
       </c>
       <c r="FC2" t="n">
-        <v>4.699492706095043e-07</v>
+        <v>0.06212453916668892</v>
       </c>
       <c r="FD2" t="n">
-        <v>5.083195446786704e-07</v>
+        <v>0.01207172498106956</v>
       </c>
       <c r="FE2" t="n">
-        <v>3.791067513247981e-07</v>
+        <v>0.004977067466825247</v>
       </c>
       <c r="FF2" t="n">
-        <v>7.380143074442458e-07</v>
+        <v>0.001550378277897835</v>
       </c>
       <c r="FG2" t="n">
-        <v>1.503799239799264e-06</v>
+        <v>0.1607794761657715</v>
       </c>
       <c r="FH2" t="n">
-        <v>4.631281171896262e-06</v>
+        <v>0.2027624249458313</v>
       </c>
       <c r="FI2" t="n">
-        <v>6.252957973629236e-07</v>
+        <v>0.2514262497425079</v>
       </c>
       <c r="FJ2" t="n">
-        <v>3.649385234893998e-06</v>
+        <v>0.2443700134754181</v>
       </c>
       <c r="FK2" t="n">
-        <v>2.608967406558804e-06</v>
+        <v>0.07663228362798691</v>
       </c>
       <c r="FL2" t="n">
-        <v>2.224645413662074e-06</v>
+        <v>0.1403767466545105</v>
       </c>
       <c r="FM2" t="n">
-        <v>2.001529992412543e-06</v>
+        <v>0.1370631456375122</v>
       </c>
       <c r="FN2" t="n">
-        <v>8.100167292468541e-07</v>
+        <v>0.08089987933635712</v>
       </c>
       <c r="FO2" t="n">
-        <v>1.580579237270285e-06</v>
+        <v>0.5204241871833801</v>
       </c>
       <c r="FP2" t="n">
-        <v>7.467054274457041e-06</v>
+        <v>0.1784601807594299</v>
       </c>
       <c r="FQ2" t="n">
-        <v>5.369371137931012e-06</v>
+        <v>0.2613246440887451</v>
       </c>
       <c r="FR2" t="n">
-        <v>2.308399587036547e-07</v>
+        <v>0.05352082103490829</v>
       </c>
       <c r="FS2" t="n">
-        <v>1.651900674914941e-06</v>
+        <v>0.5186077952384949</v>
       </c>
       <c r="FT2" t="n">
-        <v>2.195393108195276e-06</v>
+        <v>0.09283511340618134</v>
       </c>
       <c r="FU2" t="n">
-        <v>1.200508563670155e-06</v>
+        <v>0.4739401042461395</v>
       </c>
       <c r="FV2" t="n">
-        <v>1.212611641676631e-05</v>
+        <v>0.5859800577163696</v>
       </c>
       <c r="FW2" t="n">
-        <v>5.320078798831673e-06</v>
+        <v>0.6198782324790955</v>
       </c>
       <c r="FX2" t="n">
-        <v>2.25535586650949e-06</v>
+        <v>0.1879492402076721</v>
       </c>
       <c r="FY2" t="n">
-        <v>6.899260370119009e-06</v>
+        <v>0.1578491926193237</v>
       </c>
       <c r="FZ2" t="n">
-        <v>6.698894026158086e-07</v>
+        <v>0.1302351653575897</v>
       </c>
       <c r="GA2" t="n">
-        <v>7.617085884703556e-06</v>
+        <v>0.05537721514701843</v>
       </c>
       <c r="GB2" t="n">
-        <v>4.231662842357764e-08</v>
+        <v>0.08165884017944336</v>
       </c>
       <c r="GC2" t="n">
-        <v>4.547125172393862e-06</v>
+        <v>0.1884956806898117</v>
       </c>
       <c r="GD2" t="n">
-        <v>5.624478944810107e-06</v>
+        <v>0.03768279403448105</v>
       </c>
       <c r="GE2" t="n">
-        <v>5.502164185600122e-06</v>
+        <v>0.187605693936348</v>
       </c>
       <c r="GF2" t="n">
-        <v>1.048925355462416e-06</v>
+        <v>0.00259154848754406</v>
       </c>
       <c r="GG2" t="n">
-        <v>2.280168018842232e-06</v>
+        <v>0.0001793503761291504</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>0.0005339873023331165</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.00577003788203001</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.009972292929887772</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.002329596318304539</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.002817613072693348</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.002861461602151394</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.003857326461002231</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.003094085957854986</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.007074814755469561</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.001253900583833456</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.00106581998988986</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.01133341714739799</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.0009316352079622447</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.0003537731245160103</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.0006551229162141681</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.008456586860120296</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>0.001785991713404655</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.003099293448030949</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.005089106969535351</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.003915475215762854</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.001143365516327322</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.000332648167386651</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.004286228213459253</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.002975717186927795</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>0.002973842434585094</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>0.001916967332363129</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>0.0002656503347679973</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>0.001593389082700014</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>0.01003412436693907</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>0.007609506137669086</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>0.006858100183308125</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>0.0009536378784105182</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>0.001848230371251702</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>0.005749431904405355</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>0.006131785456091166</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>0.0003023348981514573</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.002818404231220484</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>0.0031920550391078</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>0.004174773581326008</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>0.002660205820575356</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>0.004550876095890999</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>0.00245367456227541</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>0.001524029765278101</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>0.008973554708063602</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>0.00407386664301157</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>0.005016370676457882</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>0.01306485757231712</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>0.005329530220478773</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>0.00573790492489934</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>0.01276730000972748</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>0.003083976916968822</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>0.001525334664620459</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>0.003999648150056601</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>0.002674751216545701</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>0.005106627475470304</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>0.01028099469840527</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>0.005996573716402054</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>0.001322594936937094</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>0.009148144163191319</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>0.007043858524411917</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>0.0008279044413939118</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>0.00290580652654171</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>0.00355522776953876</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>0.0007119259680621326</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>0.000875533209182322</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>0.001522222650237381</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>0.003718673018738627</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>0.003871468361467123</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>0.00258537894114852</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>0.001155311474576592</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>0.0002232440747320652</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>0.0007907579420134425</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>0.003440893953666091</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>0.008458420634269714</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>0.0002794750034809113</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>0.00145518803037703</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>0.005507531575858593</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>0.0004932830343022943</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>0.004430246539413929</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>0.002922306302934885</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>0.004022995010018349</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>6.404385203495622e-05</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>0.001052905688993633</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>0.003552074078470469</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>0.004290773998945951</v>
       </c>
       <c r="CH3" t="n">
-        <v>0</v>
+        <v>0.001914369408041239</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>0.000950869987718761</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>0.0001532156602479517</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>0.001354144886136055</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>0.0007693659281358123</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>0.00040972582064569</v>
       </c>
       <c r="CN3" t="n">
-        <v>0</v>
+        <v>0.01432276330888271</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>0.007670356426388025</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>0.01087583880871534</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0</v>
+        <v>0.01208323054015636</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>0.004125237930566072</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>0.002751288469880819</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>0.005934929009526968</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>0.002469324041157961</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>0.0007920627249404788</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>0.0004368957015685737</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>0.003680777736008167</v>
       </c>
       <c r="CY3" t="n">
-        <v>0</v>
+        <v>0.003662648610770702</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>0.002650535199791193</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>3.893278699251823e-05</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>0.0008808339480310678</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>0.0004135436611250043</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>0.001768897753208876</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>0.001779950223863125</v>
       </c>
       <c r="DF3" t="n">
-        <v>0</v>
+        <v>0.001632744329981506</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>0.003471644595265388</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>0.003959671128541231</v>
       </c>
       <c r="DI3" t="n">
-        <v>0</v>
+        <v>0.007285371422767639</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>0.00217023678123951</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>0.006435457617044449</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>0.008027892559766769</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>0.002136619295924902</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>0.002156633883714676</v>
       </c>
       <c r="DO3" t="n">
-        <v>0</v>
+        <v>0.0007922233780846</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>0.0006275331834331155</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>0.00357378413900733</v>
       </c>
       <c r="DR3" t="n">
-        <v>0</v>
+        <v>0.005226091481745243</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>0.001203671097755432</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>0.001800983678549528</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>0.005460295360535383</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>0.003036608686670661</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>0.0004332215758040547</v>
       </c>
       <c r="DX3" t="n">
-        <v>0</v>
+        <v>0.001222907099872828</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>0.001106188865378499</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>0.004716543946415186</v>
       </c>
       <c r="EA3" t="n">
-        <v>0</v>
+        <v>0.002266043797135353</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>0.0004491468425840139</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>0.008362610824406147</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>0.00213380204513669</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>0.005542895756661892</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>0.003293926129117608</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>0.0008736829622648656</v>
       </c>
       <c r="EH3" t="n">
-        <v>0</v>
+        <v>0.003653165651485324</v>
       </c>
       <c r="EI3" t="n">
-        <v>0</v>
+        <v>0.001862347708083689</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0</v>
+        <v>0.002950018737465143</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>0.003043377073481679</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>0.002160738687962294</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>0.001371414167806506</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>0.003609433071687818</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>0.001828031148761511</v>
       </c>
       <c r="EP3" t="n">
-        <v>0</v>
+        <v>0.001912350067868829</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0</v>
+        <v>0.001685509458184242</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>0.0006302245892584324</v>
       </c>
       <c r="ES3" t="n">
-        <v>0</v>
+        <v>0.00548485666513443</v>
       </c>
       <c r="ET3" t="n">
-        <v>0</v>
+        <v>0.009843521751463413</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>0.0002966166939586401</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>0.0008739649783819914</v>
       </c>
       <c r="EW3" t="n">
-        <v>0</v>
+        <v>0.0008226452628150582</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>0.0005752651486545801</v>
       </c>
       <c r="EY3" t="n">
-        <v>0</v>
+        <v>0.0004439287004061043</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0</v>
+        <v>0.003939485177397728</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>0.00331041356548667</v>
       </c>
       <c r="FB3" t="n">
-        <v>0</v>
+        <v>0.004073664080351591</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>0.0002949222107417881</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>0.001256190938875079</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>0.0006172541761770844</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>0.0003495138371363282</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>0.001769273309037089</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>0.002393702510744333</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>0.004426022991538048</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>0.00113022536970675</v>
       </c>
       <c r="FK3" t="n">
-        <v>0</v>
+        <v>0.006223131436854601</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>0.003850216744467616</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>0.006242168135941029</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>0.004549912642687559</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>0.0008678974118083715</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>0.01014182902872562</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>0.006427872460335493</v>
       </c>
       <c r="FR3" t="n">
-        <v>0</v>
+        <v>0.009369629435241222</v>
       </c>
       <c r="FS3" t="n">
-        <v>0</v>
+        <v>0.00583320390433073</v>
       </c>
       <c r="FT3" t="n">
-        <v>0</v>
+        <v>0.003400974906980991</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>0.01482908055186272</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>0.001363139133900404</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>0.01101461891084909</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>0.002433099551126361</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>7.417355664074421e-05</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0</v>
+        <v>0.0003716752398759127</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>0.007517656777054071</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>0.003633156884461641</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>0.0005132644437253475</v>
       </c>
       <c r="GD3" t="n">
-        <v>0</v>
+        <v>0.0006846412434242666</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>0.001972414553165436</v>
       </c>
       <c r="GF3" t="n">
-        <v>0</v>
+        <v>0.002772783860564232</v>
       </c>
       <c r="GG3" t="n">
+        <v>0.002546715084463358</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.06772056967020035</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.3346975445747375</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.06746000051498413</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.03988314419984818</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.06078793853521347</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1029189974069595</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001356067135930061</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.04785799980163574</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.005809307098388672</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.03604626655578613</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.3949126899242401</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.08986048400402069</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.09965869039297104</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1201869398355484</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.08402837067842484</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.04468566179275513</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.005659434013068676</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.01700745150446892</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.0001021334901452065</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.01703081093728542</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.006780590862035751</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.04213980212807655</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.03810030594468117</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.03368309140205383</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.0380735918879509</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.08229488879442215</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.04143085703253746</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.004678145982325077</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.045870341360569</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.01718101277947426</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.07814224809408188</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.04477745294570923</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.02013524621725082</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.03416259586811066</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.07607107609510422</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.03863059729337692</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.004456386901438236</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.07196719944477081</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.03738827258348465</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.00230812095105648</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.07775814086198807</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.02328624203801155</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.05017323046922684</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.02689361572265625</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.01964728720486164</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.002653368748724461</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.2572421729564667</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.01247968152165413</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.004335741512477398</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.05404969677329063</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.121668316423893</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.02235064283013344</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.04229869320988655</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.03209606558084488</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.0036143958568573</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.02658448927104473</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.05211574584245682</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0.001226589782163501</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.03983776271343231</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0.03386915102601051</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0.02999754063785076</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.04262486100196838</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.03342139720916748</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.003358647227287292</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.01452856510877609</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0.01267299707978964</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.003217458724975586</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0.02812869474291801</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0.02182232774794102</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0.02787569537758827</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0.005546563304960728</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0.00407855212688446</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0.007414269261062145</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0.1658854633569717</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0.0385097861289978</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0.004789078608155251</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0.01350010745227337</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0.09235044568777084</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0.02280624024569988</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>0.02259844914078712</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.03168897703289986</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0.008161240257322788</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.1117070987820625</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.01860892958939075</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.01158082764595747</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0.01562109589576721</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.04566352814435959</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.008864904753863811</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.01746913231909275</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>0.008743026293814182</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>0.0839536115527153</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>0.1606615632772446</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>0.06062832102179527</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>1.971051096916199e-05</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>0.02549704164266586</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>0.07223010063171387</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>0.02414861135184765</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>0.01102513447403908</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>0.01008312590420246</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>0.0006259018555283546</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>0.1076426357030869</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>0.01672850549221039</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>0.02056531421840191</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>0.01582017168402672</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>0.04553256928920746</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>0.001021204050630331</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>0.007420848589390516</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>0.009673992171883583</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>0.04220627620816231</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>0.01303251087665558</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0.005105351097881794</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>0.0008721407502889633</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>0.0360923707485199</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>0.04790574684739113</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>0.0102869737893343</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0.002065357752144337</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>0.01191569864749908</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>0.02465129643678665</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>0.07079648971557617</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>0.02427793480455875</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>0.01597650907933712</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>0.01159198395907879</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0.0004827437223866582</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>0.0178222618997097</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>0.05199984088540077</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>0.0275792945176363</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0.0009421017020940781</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>0.05163202062249184</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>8.838710346026346e-05</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>0.01446117088198662</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>0.01703934371471405</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>0.05501727014780045</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>0.009636889211833477</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>0.005191999953240156</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>0.03087681531906128</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>0.01858880743384361</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>0.07031086087226868</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>0.009445310570299625</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>0.02721617743372917</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>0.01251272857189178</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>0.02370095998048782</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>0.003933041356503963</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>0.00761695858091116</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>0.003384904703125358</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>0.00819005910307169</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>0.05965447053313255</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>0.009103616699576378</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>0.01028881035745144</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>0.01565039716660976</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>0.01517851650714874</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>0.02497326582670212</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>0.03857103735208511</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>0.007569208741188049</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>0.002121349098160863</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>0.1184948682785034</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>0.01652105525135994</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>0.01161207910627127</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>0.008780686184763908</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>0.04625052213668823</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>0.01493271254003048</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>0.001334490953013301</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>0.010039446875453</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>0.01435845717787743</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>0.02258883416652679</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>0.01335543021559715</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>0.02684064954519272</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>0.02897347882390022</v>
+      </c>
+      <c r="FL4" t="n">
+        <v>0.03556262701749802</v>
+      </c>
+      <c r="FM4" t="n">
+        <v>0.01865650713443756</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>0.01940808445215225</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>0.02165299281477928</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>0.04644963890314102</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>0.09662981331348419</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>0.00240662507712841</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>0.008080363273620605</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>0.05169592425227165</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>0.07436040043830872</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>0.04452904313802719</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>0.07023907452821732</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>0.05531946569681168</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>0.0107167586684227</v>
+      </c>
+      <c r="FZ4" t="n">
+        <v>0.05243740230798721</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>0.001847661100327969</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>0.01029513869434595</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>0.019854336977005</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>0.01132321916520596</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>0.07863114029169083</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>0.003364921314641833</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>0.03387702628970146</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.005205188877880573</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.006006025243550539</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.01207530219107866</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.01325314678251743</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.005731024779379368</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.01257404405623674</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.007999379187822342</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.02289626002311707</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.00515476893633604</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0003408812917768955</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.01495296135544777</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.006284633651375771</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.02587961032986641</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0001255300594493747</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.02123977988958359</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.001804134342819452</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.01805166900157928</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.006455755792558193</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.001341499271802604</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.002699072938412428</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.004119435325264931</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.01167680788785219</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.001200620085000992</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.004461867269128561</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.002610149327665567</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.001130757969804108</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.0003732709446921945</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.00300385314039886</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.006584904622286558</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.00292500713840127</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.006175512447953224</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.001149913878180087</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.002320878440514207</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.004967570304870605</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.00262733525596559</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.0002521719725336879</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.01083937846124172</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.003405959345400333</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.00918662641197443</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.006772790104150772</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.007421295158565044</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.007828433066606522</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.001132136094383895</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.002357636578381062</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.003845673520117998</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.01886079087853432</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.01697936095297337</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.01328756287693977</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.01147303357720375</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.005934800021350384</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.01495196018368006</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.001027488149702549</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.009091696701943874</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.0004334840923547745</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.01551062613725662</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.01268605701625347</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.001738515333272517</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0.0144723579287529</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0.02145543321967125</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0.002247143071144819</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0.004128118511289358</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.0054469951428473</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.001371733262203634</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.002335620578378439</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.00118873012252152</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0.006385369226336479</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0.001768733491189778</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0.001691068988293409</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0.006805123761296272</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0.002422036835923791</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0.005349523387849331</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0.003809301648288965</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0.01145736873149872</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0.003750188043341041</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0.004748958628624678</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0.01324963476508856</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0.002691608853638172</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0.005049096886068583</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0.008499009534716606</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0.01251114718616009</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0.001435443293303251</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0.003966397605836391</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0.002881659893319011</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0.005760634317994118</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.002227356191724539</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.001891900785267353</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0.002790292724967003</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.002086476655676961</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.006145098712295294</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>4.947971319779754e-05</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0.0009640619391575456</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0.003479124046862125</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0.01858632266521454</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0.007881775498390198</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>0.009173106402158737</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0.003919343929737806</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>0.007891746237874031</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0.01199227385222912</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>0.006607233546674252</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0.004861160181462765</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0.0004574870690703392</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>0.0028563744854182</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>0.003477718681097031</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0.003922967705875635</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>0.004632527008652687</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>0.0007865320076234639</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0.007231335155665874</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>2.639656304381788e-05</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0.008812556974589825</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>0.005763835273683071</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0.008902626112103462</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0.005711834412068129</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>0.004460353404283524</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>0.0004349093651399016</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>0.01219391264021397</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0.01065920386463404</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>0.0004884121008217335</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0.002995009766891599</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>0.0008976103272289038</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>0.01077895797789097</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>0.008803261443972588</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>0.005369839258491993</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0.009374924004077911</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0.001845213584601879</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0.001046995283104479</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>0.0001237738761119545</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>0.004864886868745089</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>0.005244013853371143</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>0.004356137942522764</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>0.008034409955143929</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>0.003367198165506124</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>0.0130164623260498</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>0.0009868519846349955</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>0.001741353422403336</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>0.008379862643778324</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>0.003032559296116233</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>0.007020343560725451</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>0.002283880254253745</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>0.004248728509992361</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>0.004967208486050367</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>0.003582022618502378</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>0.002050057519227266</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>0.005344302393496037</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>0.0005981429712846875</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>0.002917657373473048</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>0.003589714411646128</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>0.0008569058263674378</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>0.003531132359057665</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>0.006645871326327324</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>0.00942921731621027</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>0.0008509395411238074</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>0.006795522291213274</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>0.002499677939340472</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>0.004363211803138256</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>0.0005316524766385555</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>0.001531356247141957</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>0.004724085796624422</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>0.002362718340009451</v>
+      </c>
+      <c r="FC5" t="n">
+        <v>0.002956217853352427</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>0.001189893810078502</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>0.00761820562183857</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>0.0004699341370724142</v>
+      </c>
+      <c r="FG5" t="n">
+        <v>0.002509839832782745</v>
+      </c>
+      <c r="FH5" t="n">
+        <v>0.0009134021238423884</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>0.00175822782330215</v>
+      </c>
+      <c r="FJ5" t="n">
+        <v>0.003113673301413655</v>
+      </c>
+      <c r="FK5" t="n">
+        <v>0.001514771953225136</v>
+      </c>
+      <c r="FL5" t="n">
+        <v>3.932934487238526e-05</v>
+      </c>
+      <c r="FM5" t="n">
+        <v>0.001145489630289376</v>
+      </c>
+      <c r="FN5" t="n">
+        <v>0.008475637994706631</v>
+      </c>
+      <c r="FO5" t="n">
+        <v>0.01031873002648354</v>
+      </c>
+      <c r="FP5" t="n">
+        <v>0.001081453170627356</v>
+      </c>
+      <c r="FQ5" t="n">
+        <v>0.02091262117028236</v>
+      </c>
+      <c r="FR5" t="n">
+        <v>0.01388120464980602</v>
+      </c>
+      <c r="FS5" t="n">
+        <v>0.02508577331900597</v>
+      </c>
+      <c r="FT5" t="n">
+        <v>0.01011784933507442</v>
+      </c>
+      <c r="FU5" t="n">
+        <v>0.01731668226420879</v>
+      </c>
+      <c r="FV5" t="n">
+        <v>0.001552570844069123</v>
+      </c>
+      <c r="FW5" t="n">
+        <v>0.02478348650038242</v>
+      </c>
+      <c r="FX5" t="n">
+        <v>0.006909153424203396</v>
+      </c>
+      <c r="FY5" t="n">
+        <v>0.001869869651272893</v>
+      </c>
+      <c r="FZ5" t="n">
+        <v>0.003318296279758215</v>
+      </c>
+      <c r="GA5" t="n">
+        <v>0.0004336454439908266</v>
+      </c>
+      <c r="GB5" t="n">
+        <v>0.001666016643866897</v>
+      </c>
+      <c r="GC5" t="n">
+        <v>0.001695076818577945</v>
+      </c>
+      <c r="GD5" t="n">
+        <v>0.004219343885779381</v>
+      </c>
+      <c r="GE5" t="n">
+        <v>0.008008602075278759</v>
+      </c>
+      <c r="GF5" t="n">
+        <v>0.004625965841114521</v>
+      </c>
+      <c r="GG5" t="n">
+        <v>0.00123186269775033</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.00747733935713768</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.003031927393749356</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.01726643741130829</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.03163701668381691</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.02191551402211189</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.003482611384242773</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.001773378811776638</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.01097459811717272</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.023570075631142e-05</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.005815411917865276</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.002494571730494499</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.01531279552727938</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.03019054606556892</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.02140370011329651</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.007312422152608633</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.01308183837682009</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.02632946893572807</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.002132953144609928</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.0009772313060238957</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.007039656396955252</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.002429127460345626</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.006630230695009232</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.002739458810538054</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.01862325519323349</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.004536539316177368</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.001996043371036649</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.003524947445839643</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.002417938550934196</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.0009154530707746744</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.007331306114792824</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.0004348433576524258</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.01714820228517056</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.0006320074899122119</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.0001172833144664764</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.01349809858947992</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.005152171477675438</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.008222763426601887</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.005696266423910856</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.008359710685908794</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.01317342184484005</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.006367768160998821</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.002378581557422876</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.0006405608728528023</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.0040436708368361</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.002140584867447615</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.01590860262513161</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.001181573141366243</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.03146305680274963</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.03536810725927353</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.02474047802388668</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.01418772712349892</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.01228244043886662</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.008550867438316345</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0.007781655061990023</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.01549478340893984</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.003485900815576315</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.008832567371428013</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0.02195238135755062</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0.0160730816423893</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0.01398790255188942</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0.003879423718899488</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.003068186342716217</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.01120346318930387</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.002811799291521311</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.007388909347355366</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.000242191250436008</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.01082069054245949</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.01107243914157152</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.003663427662104368</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0.005479402840137482</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0.004756955429911613</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0.005290722008794546</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0.003118829103186727</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0.00481354258954525</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0.01347864791750908</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0.01980271935462952</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0.01045581232756376</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0.00431289616972208</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0.006628274917602539</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0.002211834769695997</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.001836145296692848</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.001038519199937582</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.001191228628158569</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.006053025368601084</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.007843859493732452</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.004898109938949347</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.003206470282748342</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.00223931111395359</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.001702232984825969</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0.001852541230618954</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0.005190062336623669</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0.003814951283857226</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0.007250577211380005</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0.003106134943664074</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.02559478767216206</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>0.009973949752748013</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>0.003701323876157403</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0.006211721338331699</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>0.006706859916448593</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0.001887009129859507</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>0.002264834940433502</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0.004568375647068024</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>0.007322314195334911</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>0.006434019654989243</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0.00603471789509058</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>0.001896348665468395</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>0.00169488147366792</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>0.0009588634711690247</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0.009998707100749016</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>0.008340490981936455</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0.01503412704914808</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0.0007869978435337543</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0.006032766774296761</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0.01941149868071079</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0.006181748583912849</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0.01534449309110641</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>0.0002216731663793325</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>0.008964431472122669</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>0.0003298262017779052</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>0.0008010014425963163</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0.006778398528695107</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0.01078645326197147</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0.0008602715097367764</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0.0008380364160984755</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0.0002344376407563686</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>0.003200586652383208</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0.013975421898067</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>0.0001680126879364252</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>0.006202741991728544</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>0.007739922031760216</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>0.006912966724485159</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>0.008632450364530087</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>0.004920640029013157</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>0.01288897171616554</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>0.009943746961653233</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>0.0009303289116360247</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>0.0006673347670584917</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>0.0009011275251396</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>0.00472453935071826</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>0.006763009820133448</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>0.002579642226919532</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>0.002622916828840971</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>0.002653721952810884</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>0.002084621693938971</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>0.002641899278387427</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>0.002540936693549156</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>0.0007709661149419844</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>0.005310396663844585</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>0.003882559947669506</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>0.01291064545512199</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>0.003162093926221132</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>0.003361980663612485</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>0.00124009104911238</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>0.001210265909321606</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>0.002000030130147934</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>0.005230233073234558</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>0.008986357599496841</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>0.006058307364583015</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>0.004529915750026703</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>0.00270290463231504</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>0.004621811676770449</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>0.0004819947062060237</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>0.002753358334302902</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>0.003119524568319321</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0.007187368348240852</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>0.008869601413607597</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>0.003646427765488625</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0.006151658482849598</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>0.004445688799023628</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>0.008671142160892487</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0.002707646228373051</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>0.006674180738627911</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>0.01343178283423185</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>0.001108902739360929</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>0.01365353725850582</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>0.009215189144015312</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>0.003206119872629642</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>0.01546953618526459</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0.009905638173222542</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>0.004342327825725079</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>0.00422479584813118</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>0.005588467698544264</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>0.003522350452840328</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>0.008149591274559498</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>0.01094484515488148</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0.008895223960280418</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>0.009327482432126999</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>0.001124338479712605</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>0.001710384851321578</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.001790279522538185</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.003688742872327566</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.000583929882850498</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.0004651581111829728</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0008463736157864332</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.002539864042773843</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0003528667148202658</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0002672059345059097</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.0001207265595439821</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.001407589297741652</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.004643495660275221</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0008643011096864939</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0004380634054541588</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.000487887067720294</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.00268184719607234</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0007244602311402559</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.00127212586812675</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.0008654560660943389</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.0002852457691915333</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.0004397050361149013</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.0006057666032575071</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.0008231980027630925</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.0004300224536564201</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.0001369314850308001</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.0001651814964134246</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.0008364314562641084</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.959508831030689e-05</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.0003450211079325527</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.0005115652456879616</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.0001166937290690839</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.0007789571536704898</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.001345994765870273</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.0005991697544232011</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.0004430835542734712</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.001205305568873882</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.0003860403667204082</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.0001160674437414855</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.00052090227836743</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.0007934963214211166</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.0008070198819041252</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.0002451623440720141</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.0004905303940176964</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.000546191877219826</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.000642626138869673</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.0001105126430047676</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0.0007406559307128191</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.003700037021189928</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.0004784147022292018</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.0004459850606508553</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0.0007807288784533739</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0.001293519395403564</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4.5290871639736e-06</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0.0001406459632562473</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.0004128508444409817</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.0001389228564221412</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>6.932857650099322e-05</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0.0005032316548749804</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0.0004402265185490251</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>9.597654570825398e-05</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0.0006796523230150342</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0.0003987026284448802</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.0006777086528018117</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.0001187747693620622</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>8.952346979640424e-05</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.001162173342891037</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0.0001890879357233644</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0.0002111105713993311</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0.001014535315334797</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0.0007624379359185696</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0.001091608195565641</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0.0001445040397811681</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0.001050685648806393</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0.0001011346466839314</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0.002474180888384581</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0.0005204427288845181</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0.0008464382262900472</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0.0002732484717853367</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0.000891860225237906</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0.0006424328894354403</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>3.549642860889435e-05</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>2.151853550458327e-05</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0.0007471034186892211</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0.001037012902088463</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>1.620796501811128e-05</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0.000176946326973848</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0.0005253960844129324</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0.000706821505445987</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0.0002489767502993345</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0.0001747617934597656</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0.000153678935021162</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>5.146820330992341e-05</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0.001937713357619941</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0.0005426018033176661</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0.0007176854414865375</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0.0005763510707765818</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0.0002871708711609244</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0.0004747926141135395</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0.000662201433442533</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0.0002322436193935573</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0.0005197337595745921</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0.0009345256257802248</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>2.384081744821742e-05</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0.000101777128293179</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0.0005510572227649391</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0.0006666498957201838</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>5.407624848885462e-05</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0.0002645802160259336</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>6.541177572216839e-05</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0.0002718809992074966</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0.001098650274798274</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0.0003222909872420132</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0.0006812653155066073</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0.001232222886756063</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0.0002258627500850707</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>1.549648004584014e-05</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0.0007053603185340762</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0.0008352797012776136</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0.0001588210288900882</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>0.0006098395679146051</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0.0005436455830931664</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0.0006752281915396452</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>0.0001726812915876508</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0.000299355189781636</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>2.024634159170091e-05</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0.0003866110055241734</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0.0004536136984825134</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0.0006406511529348791</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0.0001513462339062244</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>4.406122025102377e-05</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>5.15399660798721e-05</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0.0005295937298797071</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0.0003140923799946904</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0.0003027389757335186</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0.0004550477315206081</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0.001272223191335797</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0.0006902600871399045</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>0.0001990492746699601</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0.0001862244098447263</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>4.198649548925459e-06</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>0.0007218265091069043</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0.0002377355995122343</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>7.570003799628466e-05</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>5.030607280787081e-05</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>8.373349555768073e-05</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>0.0004069918359164149</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>0.000383105652872473</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>0.0001352760591544211</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0.000651483132969588</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>0.001258738455362618</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0.0003792892093770206</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>0.000117404997581616</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>6.904797919560224e-05</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0.000813035003375262</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>0.0007532993331551552</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>0.001175470999442041</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>4.034991434309632e-05</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>8.142393198795617e-05</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>0.0007180240354500711</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0.0005307095125317574</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0.0002246912772534415</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0.0001879514893516898</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>0.0002250860852655023</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0.0003681248635984957</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>0.001082628150470555</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0.0002131703804479912</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0.0009408805053681135</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>0.0005082989810034633</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0.001410369761288166</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0.0007277054246515036</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0.001050627790391445</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0.0005527760367840528</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>9.578245226293802e-05</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>0.0009871363872662187</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0.0007208195747807622</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0.0004570236778818071</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>0.0008709204266779125</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>0.0001775709533831105</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0.0006561102345585823</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0.0005603848258033395</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>0.0004882424836978316</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0.0008298263419419527</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>0.0002576650877017528</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0.0004214482614770532</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0.000481309398310259</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0.0006444619502872229</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0.0005356803303584456</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>0.0002464414574205875</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0.0002965604653581977</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0.00083212333265692</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.01540343090891838</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.1083763539791107</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01428781170397997</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.06281396746635437</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01571859605610371</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01807905919849873</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02912325412034988</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0186004750430584</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.005811212118715048</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.003157880622893572</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.1103342622518539</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01919181644916534</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.08922114223241806</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.03934308886528015</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.007569349370896816</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.02605769224464893</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.007651516236364841</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.009112229570746422</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.004448699299246073</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.01514347642660141</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.004961179103702307</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.007049775216728449</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.01344100292772055</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.01824411191046238</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.005875892005860806</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.01277663372457027</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.01708716712892056</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.01403903961181641</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.004082862753421068</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.009754189290106297</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.02699635922908783</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.01366145350039005</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.02791433967649937</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.008790932595729828</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.01119284983724356</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.007317361421883106</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>7.058354094624519e-05</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.0326300784945488</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.007501693442463875</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.01541786175221205</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.01633392460644245</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.01589135453104973</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.006033234298229218</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.0002835312625393271</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.00174060498829931</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.00798299815505743</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.05889663100242615</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>4.497292684391141e-05</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.02060185186564922</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.05628785490989685</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.007643197197467089</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.002091090194880962</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.01083081215620041</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.00609462708234787</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.0009336601942777634</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.001389008481055498</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.0185285210609436</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.01656338945031166</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0.005910714156925678</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0.009310935623943806</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.00874263234436512</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.01954035833477974</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.01277580205351114</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.003677383065223694</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.0098619619384408</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0.001656766980886459</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.008415184915065765</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>4.29842621088028e-05</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0.003176918253302574</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.003083490766584873</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0.006451324094086885</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0.0005116192623972893</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0.00621374137699604</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.05478192865848541</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0.007177967578172684</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0.02497084811329842</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0.01549745071679354</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.0206395760178566</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0.01039010100066662</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0.003240225370973349</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.01581750810146332</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.0006035206606611609</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.0327419750392437</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0.005251501686871052</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.02627035789191723</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.0008045135764405131</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.003315286478027701</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0.0007306454936042428</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0.002363580511882901</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0.002832722151651978</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0.01162403542548418</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0.02966608107089996</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0.0269068218767643</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.0570002906024456</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.01557014882564545</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.01540463324636221</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0.00480419397354126</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0.00317191774956882</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0.01027025282382965</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0.001737499958835542</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0.03094209544360638</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0.005644770339131355</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.02566125243902206</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0.005237201694399118</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.003456725040450692</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>0.00277462974190712</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0.001330220722593367</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0.005433329381048679</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0.004608909599483013</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0.01512219477444887</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0.003223835723474622</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.01255106925964355</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.02256582677364349</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0.02819820120930672</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0.00378817948512733</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0.02525058202445507</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0.01508607156574726</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0.0002103560836985707</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>0.02206301689147949</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0.007950811646878719</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.01516376622021198</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>0.002397942589595914</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.003015947295352817</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0.008908305317163467</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0.01889955811202526</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0.02687052823603153</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0.009384861215949059</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.002006321446970105</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>0.006272223312407732</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.009046811610460281</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.006707701832056046</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0.0191107764840126</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>0.003907558042556047</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0.03843382000923157</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>0.02841831184923649</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>0.009746921248733997</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>0.02545231580734253</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0.008169458247721195</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.0214441753923893</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>0.003433274570852518</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0.002140558324754238</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0.0002334264572709799</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0.002129666972905397</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>0.004074636846780777</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>0.002551234094426036</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>0.02742719650268555</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>0.0005776844918727875</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>0.01618281565606594</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>0.008021388202905655</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0.001483992207795382</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0.009969592094421387</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>0.00586865795776248</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0.008407198823988438</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>0.003150098025798798</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>0.03511970490217209</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>0.004246378783136606</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0.02915513515472412</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>0.002740925177931786</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>0.006562137976288795</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0.003443660214543343</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0.004085898399353027</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>0.006337806582450867</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>0.002023397013545036</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>0.01565777882933617</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>0.006222465075552464</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.01293586660176516</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>0.002730529056861997</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>0.004300975240767002</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0.002672300674021244</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0.005609634332358837</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>0.01109282951802015</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>0.01611521281301975</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>0.03091191872954369</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>0.00175212137401104</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0.02174502983689308</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>0.009027153253555298</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0.009034356102347374</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>0.007005230523645878</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>0.009224267676472664</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>0.01809594221413136</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0.01308195292949677</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>0.02296721190214157</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0.00810273177921772</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>0.01623109728097916</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>0.02331637218594551</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>0.008534844033420086</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>0.02173724770545959</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>0.00161272194236517</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0.004739230498671532</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0.0295967273414135</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.3501628637313843</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.1243953257799149</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0314934141933918</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.07157687842845917</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2173932939767838</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.02850582264363766</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.00146029144525528</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.05901223421096802</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.002792730927467346</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.4978576898574829</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.1327414512634277</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.09889967739582062</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.01083533465862274</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.2615796029567719</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.1055441796779633</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.127809002995491</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.01573896408081055</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.0869680792093277</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.09507196396589279</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.02210431732237339</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.1063212603330612</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.05683938413858414</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.02268354780972004</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.04022292792797089</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.1675564497709274</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.02308123186230659</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.1100867837667465</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.01435749232769012</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.01519185956567526</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.03302997723221779</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.22092404961586</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.1002663224935532</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.06104512140154839</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.1156352907419205</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.03396286070346832</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.03133003786206245</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.06360211223363876</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.003469290677458048</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.06294190138578415</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.03904435783624649</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.03905559331178665</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.05801258608698845</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.1759197562932968</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.0391806922852993</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.03800957649946213</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.4661482870578766</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.04725358635187149</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.01171842310577631</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.02104182541370392</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0.2518218755722046</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.02877616323530674</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0.01033447310328484</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0.04380759596824646</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0.02190801873803139</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.01191833987832069</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.06157052889466286</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0.05162063986063004</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0.09632453322410583</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0.02260426059365273</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0.08781544864177704</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.01831672526896</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.007917696610093117</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.06771479547023773</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.06367466598749161</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0.01739849895238876</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0.09009642899036407</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.06323423981666565</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0.04039476811885834</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0.02163951098918915</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0.07985654473304749</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0.04367781803011894</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0.06555177271366119</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0.3000564277172089</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0.01794525235891342</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0.0768076479434967</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>0.03473151847720146</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0.1103694662451744</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0.0309373177587986</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0.08547209948301315</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0.01621163822710514</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0.05408071726560593</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0.1017234697937965</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0.02408284693956375</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0.02363915182650089</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.02293085306882858</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0.08000828325748444</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0.04294466599822044</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0.02877271734178066</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0.02843927405774593</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0.001415684819221497</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0.2991610467433929</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0.01138263940811157</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0.06988978385925293</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0.002309337258338928</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0.1307340711355209</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0.06082800775766373</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0.01159991510212421</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>0.07848578691482544</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0.036602433770895</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>0.0987134575843811</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0.02308487519621849</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0.02769497968256474</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0.03519570827484131</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0.07950267195701599</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0.01123867742717266</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0.02053001523017883</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0.03928849101066589</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0.04046236723661423</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>0.06289670616388321</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0.01251744106411934</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0.0669417530298233</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0.161238819360733</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0.004126179963350296</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0.09470479190349579</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0.01346622966229916</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0.05191325768828392</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0.02804364077746868</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>0.07043516635894775</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0.003436123952269554</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0.1166115626692772</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>0.08205219358205795</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0.0279222447425127</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0.03451641276478767</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0.1592410355806351</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0.01469241827726364</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0.07832132279872894</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>0.005723338108509779</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0.08106577396392822</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>0.02713351510465145</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0.08736193180084229</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0.1322680562734604</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>0.02086658403277397</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0.03198317438364029</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>0.07958446443080902</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>0.03867045789957047</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>0.02900461480021477</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>0.002753892913460732</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0.03409162536263466</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>0.08633090555667877</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0.01639315113425255</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0.04276503622531891</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>0.06401873379945755</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>0.02733205258846283</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>0.02572822570800781</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>0.01419187895953655</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>0.01119647733867168</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>0.08654021471738815</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>0.09163229167461395</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0.02477875724434853</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>0.05661782622337341</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0.006269589066505432</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0.03280622512102127</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>0.05522317066788673</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>0.1182997226715088</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>0.02356959320604801</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>0.02208524383604527</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>0.05182333290576935</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0.08147221803665161</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0.05098803341388702</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0.009216459468007088</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>0.04048960655927658</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0.02600875124335289</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>0.1180513352155685</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0.04096759110689163</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>0.1127707436680794</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>0.05834369361400604</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0.03515522927045822</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0.07954154908657074</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0.1245709583163261</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0.05574361979961395</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0.03343628346920013</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>0.05774383991956711</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0.00957893580198288</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>0.1757777184247971</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>0.001808799803256989</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>0.0110850790515542</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>0.09564016759395599</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0.03251820802688599</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>0.05952256172895432</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0.100206583738327</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>0.034407839179039</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0.01425956841558218</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>0.07629943639039993</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>0.003027074038982391</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0.01967634074389935</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0.03387864679098129</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>0.03619413450360298</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0.09897370636463165</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.008886630646884441</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.08719304949045181</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.006711380556225777</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.04194230958819389</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0157685074955225</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01800055615603924</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01444793771952391</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0152621790766716</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.009508154354989529</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.006682358682155609</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.09508161246776581</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.01045614387840033</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.06150022149085999</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.02798807434737682</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.01133128814399242</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.006872507743537426</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.01026378851383924</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.01059049181640148</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.003082208335399628</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.007593865972012281</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.003844681661576033</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.01444341242313385</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.01375990267843008</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.01205448433756828</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.008513892069458961</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.006160615477710962</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.01031664945185184</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.004887411370873451</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.002850012853741646</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.00659622997045517</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.01702651381492615</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.02052470855414867</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.01616965979337692</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.00460678618401289</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.01706171408295631</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.003781924257054925</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.002795575885102153</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.02396427094936371</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.005375062581151724</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.01385828852653503</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.008412771858274937</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.009951846674084663</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.00337411742657423</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.005098882596939802</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.001949667930603027</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.003954394720494747</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.07582306116819382</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.002956729149445891</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.01397771295160055</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.03142577037215233</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.01156034413725138</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.004667235072702169</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.01071105618029833</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.002971173264086246</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.003774504642933607</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.003630834631621838</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.01148682739585638</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0.009663260541856289</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.001692484365776181</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.00653769401833415</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0.002317091450095177</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.01166138611733913</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.008357095532119274</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.002254076534882188</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.00224823784083128</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.0008134718518704176</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.001461419742554426</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.01165420189499855</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0.003837360301986337</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0.01735077612102032</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.216941745951772e-05</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0.0008997716940939426</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0.001996036851778626</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.04730500653386116</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0.002508445177227259</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0.02251315861940384</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0.006951671559363604</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0.01475094258785248</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0.0107945566996932</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0.003086854238063097</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0.009131168015301228</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0.000476415385492146</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.02868697047233582</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0.002887884620577097</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.01299665682017803</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.004104740917682648</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.003396275220438838</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.00208723871037364</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.001896129222586751</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0.00106619915459305</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0.01697725616395473</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.03864963352680206</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0.01995576173067093</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0.03400484472513199</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>0.003948357421904802</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>0.0126236705109477</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0.005509762093424797</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0.0002811517915688455</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0.00153850787319243</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0.002875756705179811</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0.02709127590060234</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0.003525767009705305</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0.01424687262624502</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0.004128172062337399</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0.004111199639737606</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0.0008531725616194308</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0.001938597299158573</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0.00262292311526835</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0.007980612106621265</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>0.01466772891581059</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0.002974230330437422</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0.01482463255524635</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.02124815993010998</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0.01750538684427738</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0.007951529696583748</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0.01830521039664745</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0.005377446766942739</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0.0009978929301723838</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0.01309845969080925</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0.001720796572044492</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0.002676640171557665</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>0.0003134043654426932</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0.001147427246905863</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0.007884373888373375</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0.01154784392565489</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0.01168136671185493</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0.008451439440250397</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>0.0104650380089879</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0.008717643097043037</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>0.01336507592350245</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>0.005262371152639389</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0.01139888819307089</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0.0002136636758223176</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>0.02360985241830349</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0.01563564315438271</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>0.006035011261701584</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0.01615298166871071</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>0.006232165265828371</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0.008541816845536232</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0.00524151511490345</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0.00170859124045819</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0.001064528245478868</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>0.0009315048810094595</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>0.002987400162965059</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0.002561438595876098</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0.01848864555358887</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>0.0002486289013177156</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>0.01005208864808083</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>0.002701799385249615</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0.001194439828395844</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0.005459953565150499</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0.005233305040746927</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>0.008939526043832302</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0.0006849735509604216</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0.03105275332927704</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>0.002314343117177486</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0.01631499081850052</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>0.001837702700868249</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>0.004880469758063555</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>0.003971944563090801</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>0.004353971220552921</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>0.00428246334195137</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0.001345299882814288</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>0.01344344019889832</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>0.003659726586192846</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0.01011762861162424</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>0.002623276319354773</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>0.000784767500590533</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>0.006101162172853947</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>0.001240797806531191</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>0.0005992306396365166</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>0.006687828805297613</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0.02712282165884972</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>0.008978890255093575</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0.01703909039497375</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>0.002110985573381186</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>0.005557846277952194</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>0.0002151420339941978</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>0.002186957513913512</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0.009783659130334854</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>0.004693928174674511</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>0.01536745857447386</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>0.004989412613213062</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0.01628962531685829</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>0.00948004238307476</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0.009599406272172928</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>0.02070673927664757</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>0.007738831918686628</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>0.001116414554417133</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0.04197480529546738</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.1153412535786629</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.005549169611185789</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.009100867435336113</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.03291487321257591</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1520613133907318</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.01015191711485386</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1014134138822556</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.008097116835415363</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.02093956619501114</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.1471177339553833</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.02708132378757</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.05193682014942169</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.07183259725570679</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.1661133468151093</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.0167769081890583</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.05283355712890625</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.01111604645848274</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.01013158913701773</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.05452405288815498</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.005176889710128307</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.062225591391325</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.04046208783984184</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.01858278177678585</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.009428816847503185</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.03456391394138336</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.007079911418259144</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.007119810208678246</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.02262143604457378</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.0006077733123674989</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.07111597061157227</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.1144400984048843</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.03239190950989723</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.0114267747849226</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.08410999178886414</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.01890888996422291</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.002103799022734165</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.06665368378162384</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.01149553712457418</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.006368224043399096</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.04344560205936432</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.04843086004257202</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.03289440274238586</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0.05557852983474731</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0.0169878825545311</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.01665311865508556</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.2678660750389099</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.002529657445847988</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.002581730950623751</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.0004921108484268188</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0.1059373617172241</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.007830403745174408</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>3.921450115740299e-05</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.006782462354749441</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.03061892464756966</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.09275221824645996</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0.007972341030836105</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0.03557850793004036</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0.07961342483758926</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0.006730476394295692</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0.02672312967479229</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.03165283426642418</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.0004190360195934772</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0.01293718907982111</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.03627024590969086</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0.02350075356662273</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0.01309245824813843</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0.04129999503493309</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0.003676136024296284</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0.07907543331384659</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0.02120796404778957</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0.02305988781154156</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0.03096005506813526</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.1466545462608337</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0.003217691089957952</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0.0118749663233757</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>0.0265220757573843</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0.08813393115997314</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0.02223947271704674</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>0.02052678726613522</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0.0145472539588809</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0.000494060106575489</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0.04852604120969772</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0.009211412630975246</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0.009212550707161427</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.01951586455106735</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.04799623042345047</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0.02530973218381405</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0.01854357123374939</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0.005676933098584414</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0.05774150043725967</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>0.1162616387009621</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0.01345242373645306</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>0.06945344805717468</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0.09549671411514282</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>0.06614825129508972</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>0.01086531765758991</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>0.01626951619982719</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>0.004879401065409184</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>0.01306634955108166</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>0.03811724856495857</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0.008454852737486362</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>0.004897791892290115</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>0.01868641190230846</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0.04799738898873329</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>0.008923408575356007</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>0.01757668703794479</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>0.002464041346684098</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0.05368860438466072</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>0.01856316812336445</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0.01044779270887375</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>0.01529256999492645</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>0.06856665760278702</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0.01215878780931234</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0.02321502938866615</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0.01013673562556505</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>0.05282531678676605</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0.0001983626279979944</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>0.03791434690356255</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>0.005151801276952028</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>0.04171869158744812</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>0.0152459479868412</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0.01386171486228704</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>0.007170316763222218</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>0.04075393080711365</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>0.004495784640312195</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>0.005981376394629478</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>0.01772552169859409</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>0.01290254108607769</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>0.01872453093528748</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>0.0267799124121666</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>0.02209634333848953</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>0.004680556710809469</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>0.00205958541482687</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>0.007366751320660114</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>0.01702559366822243</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>0.01851410791277885</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>0.01094838418066502</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>0.03628054261207581</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>0.01564781367778778</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>0.02051779255270958</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>0.0009474977850914001</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>0.01724201440811157</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>0.01222964376211166</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>0.001628783531486988</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>0.0200309082865715</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>0.007236365228891373</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>0.02827154844999313</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>0.01368026342242956</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>0.02683717384934425</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>0.03108843788504601</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>0.00513688288629055</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>0.005185571499168873</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>0.006540484260767698</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>0.05039266496896744</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>0.0129495607689023</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>0.003783485852181911</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>0.01700019650161266</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>0.04715986922383308</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>0.02222063578665257</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>0.01993421837687492</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>0.002707874402403831</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>0.02594494447112083</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>0.05791508406400681</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>0.00374371325597167</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>0.05467002838850021</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>0.01760575175285339</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>0.05187469720840454</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>0.02773668058216572</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>0.07724494487047195</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>0.007469616830348969</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>0.006310857832431793</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>0.05566250532865524</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>0.01993172988295555</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>0.06513754278421402</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>0.04653634130954742</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>0.09265661239624023</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>0.0225102137774229</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>0.01193482149392366</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>0.01156149804592133</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>0.01575546152889729</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>0.01039171777665615</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>0.03522223606705666</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>0.03060628846287727</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>0.01438625250011683</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>0.007382594048976898</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>0.01928619295358658</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>0.03687861561775208</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>0.01666738092899323</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0.007901977747678757</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.02896992862224579</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.008783189579844475</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.007015752606093884</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.007607481442391872</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.006861791480332613</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.009833516553044319</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.008241757750511169</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.008554537780582905</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.006336529739201069</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.03692744672298431</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.0101922582834959</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.01771515049040318</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0121775921434164</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0003449057694524527</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.002130133798345923</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.002628015587106347</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.01161080226302147</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.00193215417675674</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.003516614902764559</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.000769477803260088</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.002503125462681055</v>
+      </c>
+      <c r="W13" t="n">
+        <v>9.179546032100916e-05</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.00234528910368681</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.004061487503349781</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.0003575969894882292</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.002604465000331402</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.0004721703007817268</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.004815362393856049</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.002593554090708494</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.008336880244314671</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.003401427529752254</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.005596320144832134</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.001845127437263727</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.01127067767083645</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.001384945120662451</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.002631925977766514</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.006474048364907503</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.00379868084564805</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.0001259569689864293</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.0004332414246164262</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.004980169702321291</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.002986895386129618</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.00532581890001893</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.002085008192807436</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.00283021992072463</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.03211218863725662</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.002927067689597607</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.001681424444541335</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.01257795561105013</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.007336042355746031</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.001808147178962827</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.001472496194764972</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.001142696943134069</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0.001985636074095964</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.005250534974038601</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0.005042251665145159</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0.004519863985478878</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.0007456514285877347</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0.006709928624331951</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0.005492205265909433</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.00608396902680397</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.007803457789123058</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.0009370802436023951</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.006297762505710125</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0.003395322943106294</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.001276274328120053</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.007751591503620148</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>3.141927300021052e-05</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0.008975474163889885</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0.0014021135866642</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0.0003280295059084892</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0.0003538300516083837</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.01780226454138756</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0.00390003714710474</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0.005416445899754763</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0.0005929389735683799</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0.001213134964928031</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0.00527005922049284</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>0.001589488936588168</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0.000324516964610666</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0.0006151085253804922</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.00937504880130291</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0.003523825434967875</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.00152884132694453</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.001826400519348681</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0.0003854287497233599</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0.0005363774253055453</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0.001778739970177412</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0.001036160392686725</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0.009668410755693913</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0.01574802026152611</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0.006645744666457176</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0.008749064989387989</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>0.0007601643446832895</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>0.004136946052312851</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0.003122077323496342</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0.0004774872213602066</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>0.0002251378609798849</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>0.00220413925126195</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>0.008796005509793758</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>0.002780995797365904</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>0.003160496242344379</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>0.0003163993824273348</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>0.0009578070603311062</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0.0008108147885650396</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>0.0009404824231751263</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>0.002547406358644366</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0.004244223237037659</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>0.001642233808524907</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0.0003652652376331389</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0.005666684824973345</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0.01065747812390327</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>0.01232967805117369</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0.001600661082193255</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0.003687581978738308</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0.0005543580045923591</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0.00508349621668458</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>0.007326429709792137</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>0.0001909505517687649</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>0.007529118098318577</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>0.002224096795544028</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0.0007007102249190211</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0.0005747432005591691</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0.004522249568253756</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>0.0007533752359449863</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0.003081298898905516</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>0.003820273326709867</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>0.002729982137680054</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>2.99219973385334e-05</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>0.003898854833096266</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0.0004736619594041258</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>0.002357505727559328</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>0.01135235652327538</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>0.005601642187684774</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>4.506082041189075e-05</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>0.003287992905825377</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>0.0007470916025340557</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>0.009294695220887661</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>0.0002158963470719755</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>0.001783218118362129</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>3.728902811417356e-06</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0.0003989003598690033</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0.003400234272703528</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0.002552471589297056</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>0.00219567702151835</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>0.003792584873735905</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>0.0004000483313575387</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>0.00113315018825233</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>0.004433632828295231</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>3.021055636054371e-05</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>0.0009659356437623501</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0.001648278092034161</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>0.001068843645043671</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>0.01126475818455219</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>0.002394148148596287</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>0.003305122721940279</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>0.0009535655844956636</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>0.0003840842109639198</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>0.001164570450782776</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>0.001426210394129157</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>0.001999314874410629</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>0.001623428077436984</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>0.006176704075187445</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>0.0006331149488687515</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>0.006054509431123734</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>0.0008722285274416208</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>0.003298553405329585</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>0.001520027755759656</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>0.0003083834890276194</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0.00245251227170229</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>0.004596369806677103</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>0.005874183960258961</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>0.002675325144082308</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>0.000173116335645318</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>0.01230031903833151</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>0.005390177015215158</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>3.688689321279526e-05</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0.004532902501523495</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>5.417619831860065e-05</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>0.0008955072844401002</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>0.003472336800768971</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>0.003030025865882635</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>0.001795383752323687</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>0.001137879560701549</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>0.003903171280398965</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>0.00466953357681632</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>0.005676089320331812</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>0.001470284070819616</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0.0005411801976151764</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.00329734617844224</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.001103791641071439</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.001114423619583249</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5.327101098373532e-05</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.001320456387475133</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5.779805360361934e-05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.319329698570073e-05</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.00202141422778368</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.000478774105431512</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.003956052474677563</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.001213661627843976</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.001848586020059884</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.0008522943244315684</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.001627991441637278</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.0002210634993389249</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.000829509284812957</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.001477954559959471</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.0002137176197720692</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.0002564651367720217</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.0004477453185245395</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.0001977374486159533</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.0001690960634732619</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.0002790338767226785</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.0001163807610282674</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.0004546694399323314</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.001118652638979256</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.0009839989943429828</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.0001124513000831939</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.000314928765874356</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.001262611011043191</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.0006627261755056679</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.0004154399503022432</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.0007996698259375989</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.0006623509107157588</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.00064641929930076</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.0003427086630836129</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.0007247222238220274</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.340488961432129e-05</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.086678821593523e-05</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.0005776877515017986</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>2.710250555537641e-06</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.0004237511893734336</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.081937807612121e-05</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>3.865535836666822e-05</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.0004402979393489659</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.001996464096009731</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.0004542226670309901</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.0006370429182425141</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.001145804300904274</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.0007288899505510926</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>2.612573734950274e-05</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.0007447990938089788</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.0007660225383006036</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.0003268892760388553</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>2.199044683948159e-05</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0.001059671863913536</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0.0006338272360153496</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0.0002820415247697383</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0.0004990471643395722</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>5.298104952089489e-06</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.001198794459924102</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.0008269320242106915</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.0001281784061575308</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.0002312172728125006</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>6.356494850479066e-05</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0.0006587300449609756</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.0001598238886799663</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0.0001100641311495565</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0.000147617349284701</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>8.767715189605951e-05</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0.0001212563220178708</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0.0001752702373778448</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.001660701935179532</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0.0001931650476763025</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>9.02808242244646e-05</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0.0002439211239106953</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0.0007213125936686993</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0.0002543716400396079</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>0.0003104660427197814</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0.00110322015825659</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>9.818388207349926e-05</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0.001001360360532999</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0.0002568508207332343</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0.0008048743475228548</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>7.099946378730237e-05</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.0003539007448125631</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.0002020831452682614</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>8.489044557791203e-05</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0.0003417022817302495</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0.0001317983696935698</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>0.001108446856960654</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>8.785481622908264e-05</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0.002221955452114344</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0.001037325244396925</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0.001066816505044699</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>5.698857421521097e-05</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0.0002349531860090792</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>0.0003321415861137211</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>2.390716326772235e-05</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>0.0009996804874390364</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0.0002084800653392449</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0.0008396446937695146</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>6.678185309283435e-05</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0.0005094229127280414</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>0.0002354402968194336</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>0.0002848638978321105</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>0.0006072008400224149</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>3.406383621040732e-05</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>0.0004793980624526739</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>0.0004867514362558722</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>0.0001610336184967309</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>0.001892807427793741</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0.001107339863665402</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>0.0003091906837653369</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0.001628575613722205</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>0.0007939883507788181</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0.0001526653650216758</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>0.000177238107426092</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>9.329240128863603e-05</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0.0004039315390400589</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>0.0003725215792655945</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0.0001085237017832696</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>0.0007771655800752342</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>0.0006329413154162467</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>0.0004395970026962459</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>0.0003178687184117734</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>0.0002962378493975848</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>0.0001358271110802889</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>0.0006204155506566167</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>0.0001416715094819665</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>0.001104097347706556</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>0.0006032528472132981</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0.0008864652481861413</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>0.001251832349225879</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>0.0002686892403289676</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>0.0007812894182279706</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>4.718007403425872e-06</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>0.0006205789977684617</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>4.89842495881021e-05</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>0.0002175553381675854</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0.0001347192737739533</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>2.962122380267829e-06</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>0.0002039460523519665</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>0.0004182311822660267</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>0.0009915408445522189</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>2.117162694048602e-05</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>0.0004000315093435347</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>0.0003644197131507099</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>2.608166687423363e-05</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0.0001202312269015238</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>0.0001909692364279181</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0.0001713686069706455</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>3.528250817907974e-05</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>0.00119753263425082</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>0.0002140645665349439</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>0.0008842034148983657</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>2.131107612513006e-05</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0.0004820549511350691</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0.0001571891771163791</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>0.0002946722670458257</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>0.0005626571364700794</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0.0001071937003871426</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>0.0004921084037050605</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>0.0005610919906757772</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>0.0003452630480751395</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>0.0004556501808110625</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0.0001112945028580725</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0.0006150273256935179</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0.001062787720002234</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0.0004162645782344043</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>0.0004163657722529024</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>0.001012789434753358</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0.0003167265676893294</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>0.001046515535563231</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>0.00101430295035243</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>7.618451490998268e-06</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>0.0001970562880160287</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0.0002488247118890285</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>7.695233216509223e-05</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0.0001508491550339386</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>0.0007968402933329344</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0.0002724325167946517</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>0.0004141920071560889</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>0.0008374305907636881</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0.001321773510426283</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>0.0005689286626875401</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>0.0004840202745981514</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>0.0005595447728410363</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0.003290480002760887</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.141123428940773</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0004507628036662936</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.05776182562112808</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.03680676966905594</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1518245041370392</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.03631100058555603</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.09693513810634613</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.01716886833310127</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.01009798422455788</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.1979241073131561</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.0318613313138485</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.1257642060518265</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.003971129655838013</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.2017428874969482</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.005843351129442453</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.01624388620257378</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.05453179031610489</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.01406653039157391</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.04252107441425323</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.003216336481273174</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.04622988402843475</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.01351368986070156</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.01462535187602043</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.02242928743362427</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.0359705463051796</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.01302520744502544</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.02820008993148804</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.0138298636302352</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.002346776891499758</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.06535186618566513</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.09902957081794739</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.003975863102823496</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.0002169366925954819</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.1078341081738472</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.02232770994305611</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.01062251906841993</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.03275604918599129</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>4.422897472977638e-05</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.015227185562253</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.02446682006120682</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.02515705861151218</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.03007977269589901</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.06237144395709038</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.003749536816030741</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.01877466402947903</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.2870701253414154</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.01028412021696568</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.04406880959868431</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.02720854245126247</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0.1386539489030838</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.003306131809949875</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0.01710437797009945</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.01041416265070438</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0.005911595188081264</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0.08083761483430862</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0.005099969450384378</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0.0398838222026825</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0.03709247708320618</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0.02286626771092415</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0.01594594866037369</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.0624476931989193</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.003050995990633965</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0.02351075783371925</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.0546576976776123</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0.0305359736084938</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0.005926739424467087</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0.01836122199892998</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0.0002216729335486889</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0.07340464740991592</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0.01646754518151283</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0.03115494176745415</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0.001266916748136282</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.1267572045326233</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0.01019955612719059</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0.02722820639610291</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>0.01996007934212685</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0.07299993187189102</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0.04505838826298714</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0.01681458950042725</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0.02033632434904575</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0.01376457046717405</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>0.05340762063860893</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0.0146580096334219</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0.01578907854855061</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.002024848014116287</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0.03310767188668251</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0.01845451816916466</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0.006838308181613684</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0.0001858739415183663</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0.04598703235387802</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>0.1001042127609253</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0.04523920640349388</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0.08920552581548691</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0.02929830364882946</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0.01536146365106106</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0.002507869154214859</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0.001407189294695854</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0.000246663810685277</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>0.0268065370619297</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>0.04792720824480057</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0.01942890137434006</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0.02769107185304165</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0.01111630536615849</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0.04462094977498055</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>0.004052006173878908</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>0.001831361558288336</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0.005535742733627558</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0.02041600272059441</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>0.01737723127007484</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0.02286718785762787</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0.006575598381459713</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>0.05570270121097565</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>0.01804842799901962</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0.04288448393344879</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0.01413963176310062</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>0.05649661272764206</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0.01635205559432507</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>0.004006263799965382</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>0.01715283654630184</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0.04152931645512581</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>0.0151709234341979</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0.04056927189230919</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0.02071043476462364</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0.01008588075637817</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>0.03255387768149376</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0.01619850471615791</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>0.03833095729351044</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>0.0164266973733902</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>0.00288054347038269</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>0.01289799995720387</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>0.00285894819535315</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>0.02509808540344238</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0.03717773407697678</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>0.0719938725233078</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>0.006952723022550344</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>0.01607582159340382</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>0.01762570813298225</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>0.01165657304227352</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>0.01586952805519104</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>0.008963317610323429</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>0.0004759994335472584</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>0.01529063656926155</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>0.004827032331377268</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>0.03155503794550896</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>0.04577915370464325</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>0.01904527470469475</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>0.04012763872742653</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>0.00773351825773716</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0.007501367479562759</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0.01468182727694511</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>0.03010673820972443</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>0.007439335808157921</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>0.01850370317697525</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>0.06222371384501457</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>0.00682914350181818</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>0.02623666636645794</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>0.01623527333140373</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>0.03565440326929092</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0.01997596584260464</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>0.002323519205674529</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>0.007923447526991367</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>0.008762424811720848</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>0.01930616423487663</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0.0008280258625745773</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>0.03771987929940224</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>0.02863926626741886</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>0.06404396891593933</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0.02351828664541245</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0.01962187141180038</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0.07526402175426483</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>0.01162587758153677</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>0.01441880594938993</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>0.05171893909573555</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>0.01811109110713005</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>0.06715662032365799</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>0.02138594910502434</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>0.005705768242478371</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>0.1035436913371086</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>0.02959230728447437</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0.001948252320289612</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>0.00618731090798974</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0.0327528715133667</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>0.011818234808743</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>0.05636446923017502</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0.01450648717582226</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>0.05157880485057831</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>0.02189764566719532</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>0.002694775350391865</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG16" t="n">
         <v>0</v>
       </c>
     </row>
